--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -14,8 +14,9 @@
     <sheet name="Cap" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Front Office" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Trades" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Teams" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Notes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Teams" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Notes" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3605,6 +3606,88 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Seeded from franchise screens: owner goals, budget, cap, contracts, lines, two trade offers (both declined).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Goalie contracts (Sorokin, Varlamov) pending from the user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Varlamov sits in goalie slot 1 on the lineup screen, Sorokin in slot 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Schedule loaded from the sportsbrackets.net 2026-27 calendar PDF. It lists 83 games (42 home): 4 vs every Metropolitan club, 2 vs TOR. Reconcile against the game's calendar.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5762,6 +5845,2136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>H/A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Time (ET)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7:45p</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10/15/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10/20/2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10/22/2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10/25/2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6p</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10/27/2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8p</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10/29/2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8p</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10/31/2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>10p</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11/12/2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10p</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11/14/2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>10p</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11/17/2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11/19/2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8p</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11/21/2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11/23/2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>11/25/2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11/27/2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>11/28/2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12/11/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>12/15/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>9p</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12/16/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>9p</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>12/18/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10p</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>12/20/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>12/22/2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>12/26/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>12/27/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>12/30/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4p</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>01/02/2027</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10p</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>01/05/2027</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10p</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>01/07/2027</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>9p</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>01/09/2027</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>01/13/2027</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>01/15/2027</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>01/16/2027</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>01/18/2027</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3p</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>01/20/2027</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>01/22/2027</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>01/23/2027</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>01/26/2027</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>01/28/2027</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>01/30/2027</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>02/01/2027</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>02/03/2027</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>02/12/2027</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>02/13/2027</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>02/15/2027</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3p</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>02/18/2027</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>02/20/2027</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>02/22/2027</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>02/23/2027</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>8p</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>02/26/2027</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>02/27/2027</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>03/01/2027</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>03/04/2027</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>03/07/2027</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>03/09/2027</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>03/12/2027</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>03/13/2027</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>03/15/2027</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>03/17/2027</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>03/20/2027</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3p</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>03/21/2027</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>3p</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>03/25/2027</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>8p</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>03/27/2027</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>03/30/2027</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>04/01/2027</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>04/02/2027</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>04/04/2027</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>04/06/2027</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>7:30p</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>04/08/2027</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>04/10/2027</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>5p</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6506,74 +8719,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Seeded from franchise screens: owner goals, budget, cap, contracts, lines, two trade offers (both declined).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Goalie contracts (Sorokin, Varlamov) pending from the user.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Varlamov sits in goalie slot 1 on the lineup screen, Sorokin in slot 2.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Schedule loaded from the sportsbrackets.net 2026-27 calendar PDF. It lists 83 games (42 home): 4 vs every Metropolitan club, 2 vs TOR. Reconcile against the game's calendar.</t>
+          <t>Schedule loaded from the NHL.com official 2026-27 release: 84 games, 42 home, 42 away. The new CBA expands the season from 82 to 84; both added games are intra-division, so every Metropolitan rival is played 4 times. Opener is 09/30/2026 at TOR.</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5895,17 +5895,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>09/30/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NJD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5920,22 +5920,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NYR</t>
+          <t>NJD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>7:30p</t>
         </is>
       </c>
     </row>
@@ -5945,22 +5945,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NYR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7:30p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TBL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10/13/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TBL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7:45p</t>
+          <t>7:30p</t>
         </is>
       </c>
     </row>
@@ -6020,22 +6020,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10/15/2026</t>
+          <t>10/13/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OTT</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>7:45p</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10/17/2026</t>
+          <t>10/15/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OTT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -6070,17 +6070,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10/20/2026</t>
+          <t>10/17/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10/22/2026</t>
+          <t>10/20/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LAK</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7:30p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -6120,22 +6120,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10/25/2026</t>
+          <t>10/22/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6p</t>
+          <t>7:30p</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10/27/2026</t>
+          <t>10/25/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NSH</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8p</t>
+          <t>6p</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10/29/2026</t>
+          <t>10/27/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NSH</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6195,22 +6195,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10/31/2026</t>
+          <t>10/29/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3:30p</t>
+          <t>8p</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>10/31/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>3:30p</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NJD</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6270,22 +6270,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SJS</t>
+          <t>NJD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11/12/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAK</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11/14/2026</t>
+          <t>11/12/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>LAK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6345,22 +6345,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11/17/2026</t>
+          <t>11/14/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CBJ</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>10p</t>
         </is>
       </c>
     </row>
@@ -6370,22 +6370,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11/19/2026</t>
+          <t>11/17/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>WPG</t>
+          <t>CBJ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11/21/2026</t>
+          <t>11/19/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>WPG</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>8p</t>
         </is>
       </c>
     </row>
@@ -6420,22 +6420,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11/23/2026</t>
+          <t>11/21/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7:30p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11/25/2026</t>
+          <t>11/23/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>7:30p</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11/27/2026</t>
+          <t>11/25/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>WPG</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7:30p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -6495,17 +6495,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11/28/2026</t>
+          <t>11/27/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WPG</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -6520,22 +6520,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>11/28/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>7:30p</t>
         </is>
       </c>
     </row>
@@ -6545,17 +6545,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6570,17 +6570,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SJS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6630,12 +6630,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>1p</t>
         </is>
       </c>
     </row>
@@ -6645,17 +6645,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12/11/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12/15/2026</t>
+          <t>12/11/2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>9p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12/16/2026</t>
+          <t>12/15/2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12/18/2026</t>
+          <t>12/16/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VGK</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>9p</t>
         </is>
       </c>
     </row>
@@ -6745,22 +6745,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12/20/2026</t>
+          <t>12/18/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NYR</t>
+          <t>VGK</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>10p</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12/22/2026</t>
+          <t>12/20/2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12/26/2026</t>
+          <t>12/22/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6820,17 +6820,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12/27/2026</t>
+          <t>12/26/2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OTT</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12/30/2026</t>
+          <t>12/27/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>OTT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -6870,22 +6870,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01/02/2027</t>
+          <t>12/30/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>4p</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01/05/2027</t>
+          <t>01/02/2027</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01/07/2027</t>
+          <t>01/05/2027</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CGY</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01/09/2027</t>
+          <t>01/07/2027</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4:30p</t>
+          <t>8p</t>
         </is>
       </c>
     </row>
@@ -6970,22 +6970,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01/13/2027</t>
+          <t>01/09/2027</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>7:30p</t>
+          <t>3:30p</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01/15/2027</t>
+          <t>01/13/2027</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>7:30p</t>
         </is>
       </c>
     </row>
@@ -7020,17 +7020,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01/16/2027</t>
+          <t>01/15/2027</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NJD</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -7045,22 +7045,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01/18/2027</t>
+          <t>01/16/2027</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NSH</t>
+          <t>NJD</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01/20/2027</t>
+          <t>01/18/2027</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>NSH</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>3p</t>
         </is>
       </c>
     </row>
@@ -7095,17 +7095,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01/22/2027</t>
+          <t>01/20/2027</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7120,22 +7120,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01/23/2027</t>
+          <t>01/22/2027</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>7:30p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -7145,22 +7145,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01/26/2027</t>
+          <t>01/23/2027</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>7:30p</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01/28/2027</t>
+          <t>01/26/2027</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01/30/2027</t>
+          <t>01/28/2027</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TBL</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>02/01/2027</t>
+          <t>01/30/2027</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>TBL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>02/03/2027</t>
+          <t>02/01/2027</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>1p</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>02/12/2027</t>
+          <t>02/03/2027</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NYR</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7295,17 +7295,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>02/13/2027</t>
+          <t>02/12/2027</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYR</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>02/15/2027</t>
+          <t>02/13/2027</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>02/18/2027</t>
+          <t>02/15/2027</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NYR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>3p</t>
         </is>
       </c>
     </row>
@@ -7370,17 +7370,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>02/20/2027</t>
+          <t>02/18/2027</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>NYR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>02/22/2027</t>
+          <t>02/20/2027</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CBJ</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>02/23/2027</t>
+          <t>02/22/2027</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7430,12 +7430,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CBJ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>8p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -7445,22 +7445,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>02/26/2027</t>
+          <t>02/23/2027</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>8p</t>
         </is>
       </c>
     </row>
@@ -7470,17 +7470,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>02/27/2027</t>
+          <t>02/26/2027</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CBJ</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7495,17 +7495,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>03/01/2027</t>
+          <t>02/27/2027</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CBJ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>03/04/2027</t>
+          <t>03/01/2027</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VGK</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>03/07/2027</t>
+          <t>03/04/2027</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>VGK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>03/09/2027</t>
+          <t>03/07/2027</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>1p</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>03/12/2027</t>
+          <t>03/09/2027</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>03/13/2027</t>
+          <t>03/12/2027</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TBL</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>03/15/2027</t>
+          <t>03/13/2027</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TBL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>03/17/2027</t>
+          <t>03/15/2027</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7695,22 +7695,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>03/20/2027</t>
+          <t>03/17/2027</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>3p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>03/21/2027</t>
+          <t>03/20/2027</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7745,22 +7745,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>03/25/2027</t>
+          <t>03/21/2027</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>8p</t>
+          <t>3p</t>
         </is>
       </c>
     </row>
@@ -7770,22 +7770,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>03/27/2027</t>
+          <t>03/25/2027</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>7:30p</t>
+          <t>8p</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>03/30/2027</t>
+          <t>03/27/2027</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>7:30p</t>
         </is>
       </c>
     </row>
@@ -7820,17 +7820,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>04/01/2027</t>
+          <t>03/30/2027</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>04/02/2027</t>
+          <t>04/01/2027</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OTT</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>04/04/2027</t>
+          <t>04/02/2027</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MTL</t>
+          <t>OTT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>7:30p</t>
+          <t>7p</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>04/06/2027</t>
+          <t>04/04/2027</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MTL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7920,22 +7920,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>04/08/2027</t>
+          <t>04/06/2027</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NJD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>7p</t>
+          <t>7:30p</t>
         </is>
       </c>
     </row>
@@ -7945,20 +7945,45 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>04/08/2027</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>7p</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>04/10/2027</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>CBJ</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>5p</t>
         </is>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -17,6 +17,14 @@
     <sheet name="Schedule" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Teams" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Notes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Games" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Scoring" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Goalie Game Log" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Opp Goaltending" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Skater Game Log" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Recaps" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Inside" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Headlines" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3612,7 +3620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3680,6 +3688,1421 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>Schedule loaded from the NHL.com official 2026-27 release: 84 games, 42 home, 42 away. The new CBA expands the season from 82 to 84; both added games are intra-division, so every Metropolitan rival is played 4 times. Opener is 09/30/2026 at TOR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G1 at TOR: Skater box score pending; Horvat's goal and the three NYI minors are the only per-player figures the play-by-play supports.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AL3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="7" customWidth="1" min="26" max="26"/>
+    <col width="7" customWidth="1" min="27" max="27"/>
+    <col width="7" customWidth="1" min="28" max="28"/>
+    <col width="7" customWidth="1" min="29" max="29"/>
+    <col width="7" customWidth="1" min="30" max="30"/>
+    <col width="7" customWidth="1" min="31" max="31"/>
+    <col width="7" customWidth="1" min="32" max="32"/>
+    <col width="7" customWidth="1" min="33" max="33"/>
+    <col width="7" customWidth="1" min="34" max="34"/>
+    <col width="7" customWidth="1" min="35" max="35"/>
+    <col width="8" customWidth="1" min="36" max="36"/>
+    <col width="8" customWidth="1" min="37" max="37"/>
+    <col width="9" customWidth="1" min="38" max="38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H/A</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>P1 F</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>P1 A</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>P2 F</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>P2 A</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>P3 F</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>P3 A</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OT F</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OT A</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SO F</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>SO A</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Shots F</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Shots A</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Hits F</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Hits A</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>TOA F</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>TOA A</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Pass% F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Pass% A</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>FOW F</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>FOW A</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>PIM F</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>PIM A</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>PP F</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>PP A</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>PPM F</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>PPM A</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>SHG F</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>SHG A</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
+      <c r="Y2" s="2" t="n"/>
+      <c r="Z2" s="2" t="n"/>
+      <c r="AA2" s="2" t="n"/>
+      <c r="AB2" s="2" t="n"/>
+      <c r="AC2" s="2" t="n"/>
+      <c r="AD2" s="2" t="n"/>
+      <c r="AE2" s="2" t="n"/>
+      <c r="AF2" s="2" t="n"/>
+      <c r="AG2" s="2" t="n"/>
+      <c r="AH2" s="2" t="n"/>
+      <c r="AI2" s="2" t="n"/>
+      <c r="AJ2" s="2" t="n"/>
+      <c r="AK2" s="2" t="n"/>
+      <c r="AL2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OTL</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>32</v>
+      </c>
+      <c r="S3" t="n">
+        <v>43</v>
+      </c>
+      <c r="T3" t="n">
+        <v>28</v>
+      </c>
+      <c r="U3" t="n">
+        <v>37</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0/2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>04:48</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>OT1</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0-0-1</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Gut punch OTL on the road to start the year. Isles look strong all game but wither when it counts.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Scorer</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B. Horvat</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>B. Duhaime</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>J. Roslovic</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>GWG</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Goalie</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SV%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TOI</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Start/Relief</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>I. Sorokin</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OTL</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>65:00</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Goalie</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Catches</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SV</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SV%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>M. Stolarz</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>65:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pos</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SOG</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PIM</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Hits</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Blk</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>PPG</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>SHG</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>GWG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>FOW</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>FOL</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Horvat picks up a loose puck over the blue line and dekes Stolarz at the right post (1-0). Ekman-Larsson slashing. Nylander is hauled down on a breakaway by Holmstrom and gets a penalty shot. Sorokin turns him away at the right post. Romanov slashing with two minutes left. Pelech slashes Paul with 7 seconds left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Nylander for slashing, 4-on-4 for 1:14. Barzal for slashing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Duhaime gets a late break in the slot and has hands in close (1-1) with 3 minutes left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Roslovic rebounds himself at the right post for the winner (2-1).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Bullet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NYI led &lt;b&gt;1-0&lt;/b&gt; after the 1st in G1 at TOR and did not score again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Toronto put &lt;b&gt;32 of its 43 shots (74%)&lt;/b&gt; on Sorokin after the first intermission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Isles killed all &lt;b&gt;3&lt;/b&gt; Toronto power plays and went &lt;b&gt;0 for 2&lt;/b&gt; on their own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Toronto out-hit NYI &lt;b&gt;37-28&lt;/b&gt; and completed &lt;b&gt;88.1%&lt;/b&gt; of its passes to the Isles' &lt;b&gt;71.6%&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fig</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kicker</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tone</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>41</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Saves</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Sorokin&lt;/b&gt; faced &lt;b&gt;43&lt;/b&gt; shots in G1 at TOR and was beaten only in the last 3 minutes of regulation and in overtime.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Goals</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Horvat&lt;/b&gt; picked up a loose puck over the blue line and deked Stolarz at the right post to open the scoring.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Penalty shot stopped</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Nylander&lt;/b&gt; was hauled down by &lt;b&gt;Holmstrom&lt;/b&gt; on a breakaway in the 1st, and Sorokin turned him away at the right post.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Slashing minors</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Romanov&lt;/b&gt;, &lt;b&gt;Pelech&lt;/b&gt; and &lt;b&gt;Barzal&lt;/b&gt; each took one in G1 at TOR, and Toronto came away with nothing on the power play.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -4921,7 +6344,6 @@
           <t>SCR</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>C. Ritchie</t>
@@ -4942,7 +6364,6 @@
           <t>SCR</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>T. DeAngelo</t>
@@ -4963,7 +6384,6 @@
           <t>SCR</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>K. MacLean</t>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -4955,7 +4955,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Toronto out-hit NYI &lt;b&gt;37-28&lt;/b&gt; and completed &lt;b&gt;88.1%&lt;/b&gt; of its passes to the Isles' &lt;b&gt;71.6%&lt;/b&gt;.</t>
+          <t>The Isles won &lt;b&gt;21 of 37 faceoffs (57%)&lt;/b&gt; in G1 at TOR and were out-hit &lt;b&gt;37-28&lt;/b&gt;.</t>
         </is>
       </c>
     </row>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -13,18 +13,18 @@
     <sheet name="Budget" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cap" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Front Office" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Trades" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Teams" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Notes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Games" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Scoring" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Goalie Game Log" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Opp Goaltending" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Skater Game Log" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Recaps" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Inside" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Headlines" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Schedule" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Teams" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Notes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Games" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Scoring" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Goalie Game Log" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Opp Goaltending" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Skater Game Log" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Recaps" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Inside" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Headlines" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Transactions" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3620,100 +3620,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Seeded from franchise screens: owner goals, budget, cap, contracts, lines, two trade offers (both declined).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Goalie contracts (Sorokin, Varlamov) pending from the user.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Varlamov sits in goalie slot 1 on the lineup screen, Sorokin in slot 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Schedule loaded from the NHL.com official 2026-27 release: 84 games, 42 home, 42 away. The new CBA expands the season from 82 to 84; both added games are intra-division, so every Metropolitan rival is played 4 times. Opener is 09/30/2026 at TOR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>09/30/2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>G1 at TOR: Skater box score pending; Horvat's goal and the three NYI minors are the only per-player figures the play-by-play supports.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4140,7 +4046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4328,7 +4234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4470,7 +4376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4602,7 +4508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4762,7 +4668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4890,7 +4796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4964,7 +4870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5103,6 +5009,186 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>active</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Trade offer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Incoming</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NYI 2027 R3; I. George (D, $0.915M)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TOR 2027 R4; TBL 2027 R4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Declined</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Trade offer</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Incoming</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>COL 2028 R3; J. Nurmi (LW, $0.870M)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>STL 2028 R4; STL 2028 R7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Declined</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Incoming</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>N. Deslauriers</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -7139,132 +7225,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Out</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>In</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TBL</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Incoming</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NYI 2027 R3; I. George (D, $0.915M)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TOR 2027 R4; TBL 2027 R4</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Declined</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>09/29/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Incoming</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>COL 2028 R3; J. Nurmi (LW, $0.870M)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>STL 2028 R4; STL 2028 R7</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Declined</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9414,7 +9374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10164,4 +10124,110 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Seeded from franchise screens: owner goals, budget, cap, contracts, lines, two trade offers (both declined).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Goalie contracts (Sorokin, Varlamov) pending from the user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Varlamov sits in goalie slot 1 on the lineup screen, Sorokin in slot 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>09/29/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Schedule loaded from the NHL.com official 2026-27 release: 84 games, 42 home, 42 away. The new CBA expands the season from 82 to 84; both added games are intra-division, so every Metropolitan rival is played 4 times. Opener is 09/30/2026 at TOR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G1 at TOR: Skater box score pending; Horvat's goal and the three NYI minors are the only per-player figures the play-by-play supports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Declined N. Deslauriers. The source screen was not captured, so the type (trade offer, signing or waivers) and the counterparty are unrecorded.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -5163,17 +5163,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Waivers</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Incoming</t>
+          <t>Claim</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Declined N. Deslauriers. The source screen was not captured, so the type (trade offer, signing or waivers) and the counterparty are unrecorded.</t>
+          <t>Passed on N. Deslauriers on waivers. A waiver claim has no trade partner, so Partner stays '-'.</t>
         </is>
       </c>
     </row>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -5003,7 +5003,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Romanov&lt;/b&gt;, &lt;b&gt;Pelech&lt;/b&gt; and &lt;b&gt;Barzal&lt;/b&gt; each took one in G1 at TOR, and Toronto came away with nothing on the power play.</t>
+          <t>&lt;b&gt;Romanov&lt;/b&gt;, &lt;b&gt;Pelech&lt;/b&gt; and &lt;b&gt;Barzal&lt;/b&gt; each took one in G1 at TOR, but Toronto came away with nothing on the power play.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -4727,7 +4727,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Horvat picks up a loose puck over the blue line and dekes Stolarz at the right post (1-0). Ekman-Larsson slashing. Nylander is hauled down on a breakaway by Holmstrom and gets a penalty shot. Sorokin turns him away at the right post. Romanov slashing with two minutes left. Pelech slashes Paul with 7 seconds left.</t>
+          <t>Horvat (1) picks up a loose puck over the blue line and dekes Stolarz at the right post (1-0). Ekman-Larsson slashing. Nylander is hauled down on a breakaway by Holmstrom and gets a penalty shot. Sorokin turns him away at the right post. Romanov slashing with two minutes left. Pelech slashes Paul with 7 seconds left.</t>
         </is>
       </c>
     </row>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -4831,7 +4831,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NYI led &lt;b&gt;1-0&lt;/b&gt; after the 1st in G1 at TOR and did not score again.</t>
+          <t>NYI carried a &lt;b&gt;1-0&lt;/b&gt; lead into the 3rd in G1 at TOR and lost it with 3 minutes to play.</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Horvat&lt;/b&gt; picked up a loose puck over the blue line and deked Stolarz at the right post to open the scoring.</t>
+          <t>&lt;b&gt;Horvat&lt;/b&gt; picked up a loose puck over the blue line and deked Stolarz at the right post in the 1st of G1 at TOR, the only puck NYI got past him.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -3620,7 +3620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4041,6 +4041,82 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1-0-1</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Six goals from six different scorers in the home opener, three of them in the first period. New Jersey's only reply came off its own rebound.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4052,7 +4128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4148,6 +4224,11 @@
           <t>B. Horvat</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>M. Kessel</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>EV</t>
@@ -4226,6 +4307,291 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>K. Palmieri</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B. Horvat</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>M. Schaefer</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>GWG</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A. Duclair</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>B. Schenn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A. Pelech</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>M. Schaefer</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>C. Cizikas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>M. Kessel</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SHG</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>J. Bratt</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>B. Schenn</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>M. Coronato</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>M. Schaefer</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PPG</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>C. Cizikas</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>M. Maccelli</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6-1</t>
         </is>
       </c>
     </row>
@@ -4674,7 +5040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4788,6 +5154,66 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Roslovic rebounds himself at the right post for the winner (2-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Horvat breaks in on the left post and goes cross slot to Palmieri (1), who one-times it from inside the hash in the left circle (1-0). Duclair (1) skates in on a delayed penalty and dekes to a backhand at the right post (2-0). Gritsyuk slashing. Noesen slashing, 5-on-3. Schenn hooking. Palmieri tripping, 5-on-3 the other way. Pageau hooking, 5-on-3 for 6 seconds. Schaefer (1) goes down broadway on the break and has hands on Rittich shorthanded (3-0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bratt rebounds himself at the right post after a flurry of shots to start the period (3-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mantha slashing. Bjugstad holding, 5-on-3. Coronato feeds Schenn (1), who finishes from above the hash in the right circle on the power play (4-1). Hischier interference. Cizikas (1) is credited after losing the puck at the side of the net and watching Bratt knock it into his own net (5-1). Maccelli (1) breaks away with two defensemen in tow and has hands down the slot on Rittich (6-1).</t>
         </is>
       </c>
     </row>
@@ -4802,7 +5228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4862,6 +5288,46 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>The Isles won &lt;b&gt;21 of 37 faceoffs (57%)&lt;/b&gt; in G1 at TOR and were out-hit &lt;b&gt;37-28&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NYI is &lt;b&gt;1-0-1&lt;/b&gt; through two games, worth &lt;b&gt;3&lt;/b&gt; of a possible 4 points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Six&lt;/b&gt; different Islanders scored in G2 vs. NJD; the team had one goal in G1 at TOR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NYI took the 1st and the 3rd &lt;b&gt;3-0&lt;/b&gt; in G2 vs. NJD and lost the 2nd &lt;b&gt;1-0&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Three straight NYI minors in the 1st of G2 vs. NJD put New Jersey two men up twice, and the only goal of that stretch went the other way.</t>
         </is>
       </c>
     </row>
@@ -4876,7 +5342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5007,6 +5473,144 @@
         </is>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Schaefer&lt;/b&gt; set up the opening goal, fed Schenn on the power play and scored shorthanded himself in G2 vs. NJD, a three-point night from a 19-year-old defenseman.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Schenn&lt;/b&gt; found Duclair at the right post in the 1st and finished Coronato's pass from above the right circle in the 3rd of G2 vs. NJD.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Goals</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Palmieri&lt;/b&gt; one-timed Horvat's cross-slot feed from the left circle to open the scoring in G2 vs. NJD, the first of six Islanders goals.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Horvat&lt;/b&gt; has a point in each of the first two games: the goal in G1 at TOR and the primary assist on Palmieri's opener in G2 vs. NJD.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Goals</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Maccelli&lt;/b&gt; outran two defensemen down the slot and beat Rittich for the last of the six in G2 vs. NJD.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Goals</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Cizikas&lt;/b&gt; was credited in the 3rd of G2 vs. NJD after he lost the puck at the side of the net and Bratt knocked it in himself.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -9380,13 +9984,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9408,6 +10015,21 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Division</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Goalie</t>
         </is>
       </c>
     </row>
@@ -9416,6 +10038,9 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9789,6 +10414,15 @@
         <is>
           <t>Metropolitan</t>
         </is>
+      </c>
+      <c r="E19" t="n">
+        <v>91</v>
+      </c>
+      <c r="F19" t="n">
+        <v>88</v>
+      </c>
+      <c r="G19" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -10132,7 +10766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10227,6 +10861,54 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G2 vs NJD: Team stats and both box scores held for the screens; the play-by-play carries the scoring, the penalties and nothing else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>G1 at TOR: Kessel credited with the assist on Horvat's goal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Team ratings (offense / defense / goaltending) come off the matchup screen and are entered per club as they are seen. NJD 91/88/80. TOR pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Owner goal 'Win the regular season home opener' evaluates 10/03/2026 and NYI won G2 6-1; status stays Open until the franchise screen shows it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -4101,6 +4101,76 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" t="n">
+        <v>35</v>
+      </c>
+      <c r="S4" t="n">
+        <v>42</v>
+      </c>
+      <c r="T4" t="n">
+        <v>40</v>
+      </c>
+      <c r="U4" t="n">
+        <v>34</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>05:44</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0/3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>W1</t>
@@ -4748,7 +4818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4866,6 +4936,48 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>65:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Rittich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>60:00</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5328,6 +5440,26 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>Three straight NYI minors in the 1st of G2 vs. NJD put New Jersey two men up twice, and the only goal of that stretch went the other way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NYI won G2 vs. NJD by five while being outshot &lt;b&gt;42-35&lt;/b&gt; and winning &lt;b&gt;14 of 46 faceoffs (30%)&lt;/b&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Isles have killed all &lt;b&gt;6&lt;/b&gt; power plays they have faced this season and are &lt;b&gt;1 for 7&lt;/b&gt; on their own, the goal coming in the 3rd of G2 vs. NJD.</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10909,6 +11041,18 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>G2 vs NJD: four team-stats screens logged (1st, 2nd, final; per-period shots and hits differenced from the cumulative screens). PP 1/5 with the only goal in the 3rd confirms Cizikas' goal was even strength. Rittich went the distance: 35 SA, 29 SV. The NYI starter is still unknown - 42 SA, 41 SV, 1 GA, W is waiting on the name.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -4676,7 +4676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4802,6 +4802,51 @@
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>I. Sorokin</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60:00</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
@@ -5615,16 +5660,16 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Saves</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Schaefer&lt;/b&gt; set up the opening goal, fed Schenn on the power play and scored shorthanded himself in G2 vs. NJD, a three-point night from a 19-year-old defenseman.</t>
+          <t>&lt;b&gt;Sorokin&lt;/b&gt; was beaten only when Bratt got to his own rebound in the 2nd of G2 vs. NJD, and has allowed three goals in two starts.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5638,7 +5683,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5647,7 +5692,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Schenn&lt;/b&gt; found Duclair at the right post in the 1st and finished Coronato's pass from above the right circle in the 3rd of G2 vs. NJD.</t>
+          <t>&lt;b&gt;Schaefer&lt;/b&gt; set up the opening goal, fed Schenn on the power play and scored shorthanded himself in G2 vs. NJD, a three-point night from a 19-year-old defenseman.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5661,16 +5706,16 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Palmieri&lt;/b&gt; one-timed Horvat's cross-slot feed from the left circle to open the scoring in G2 vs. NJD, the first of six Islanders goals.</t>
+          <t>&lt;b&gt;Schenn&lt;/b&gt; found Duclair at the right post in the 1st and finished Coronato's pass from above the right circle in the 3rd of G2 vs. NJD.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5684,16 +5729,16 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Games</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Horvat&lt;/b&gt; has a point in each of the first two games: the goal in G1 at TOR and the primary assist on Palmieri's opener in G2 vs. NJD.</t>
+          <t>&lt;b&gt;Palmieri&lt;/b&gt; one-timed Horvat's cross-slot feed from the left circle to open the scoring in G2 vs. NJD, the first of six Islanders goals.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5707,16 +5752,16 @@
         <v>2</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Games</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Maccelli&lt;/b&gt; outran two defensemen down the slot and beat Rittich for the last of the six in G2 vs. NJD.</t>
+          <t>&lt;b&gt;Horvat&lt;/b&gt; has a point in each of the first two games: the goal in G1 at TOR and the primary assist on Palmieri's opener in G2 vs. NJD.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5739,7 +5784,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Cizikas&lt;/b&gt; was credited in the 3rd of G2 vs. NJD after he lost the puck at the side of the net and Bratt knocked it in himself.</t>
+          <t>&lt;b&gt;Maccelli&lt;/b&gt; outran two defensemen down the slot and beat Rittich for the last of the six in G2 vs. NJD.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -10898,7 +10943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11053,6 +11098,18 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sorokin is the starter by default and is logged as the starting goalie in every game unless the user names Varlamov. G2: 42 SA, 41 SV, 1 GA, W.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -10821,6 +10821,15 @@
           <t>Atlantic</t>
         </is>
       </c>
+      <c r="E29" t="n">
+        <v>89</v>
+      </c>
+      <c r="F29" t="n">
+        <v>87</v>
+      </c>
+      <c r="G29" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10943,7 +10952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11110,6 +11119,18 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Team ratings: TOR 89/87/85.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -10240,6 +10240,15 @@
           <t>Pacific</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F3" t="n">
+        <v>83</v>
+      </c>
+      <c r="G3" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10262,6 +10271,15 @@
           <t>Atlantic</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>88</v>
+      </c>
+      <c r="F4" t="n">
+        <v>85</v>
+      </c>
+      <c r="G4" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10284,6 +10302,15 @@
           <t>Atlantic</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>87</v>
+      </c>
+      <c r="F5" t="n">
+        <v>87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10306,6 +10333,15 @@
           <t>Pacific</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>81</v>
+      </c>
+      <c r="F6" t="n">
+        <v>85</v>
+      </c>
+      <c r="G6" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10328,6 +10364,15 @@
           <t>Metropolitan</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F7" t="n">
+        <v>89</v>
+      </c>
+      <c r="G7" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10350,6 +10395,15 @@
           <t>Central</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>85</v>
+      </c>
+      <c r="F8" t="n">
+        <v>84</v>
+      </c>
+      <c r="G8" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10372,6 +10426,15 @@
           <t>Central</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" t="n">
+        <v>90</v>
+      </c>
+      <c r="G9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10394,6 +10457,15 @@
           <t>Metropolitan</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>87</v>
+      </c>
+      <c r="F10" t="n">
+        <v>87</v>
+      </c>
+      <c r="G10" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10416,6 +10488,15 @@
           <t>Central</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>88</v>
+      </c>
+      <c r="F11" t="n">
+        <v>89</v>
+      </c>
+      <c r="G11" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10438,6 +10519,15 @@
           <t>Atlantic</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>85</v>
+      </c>
+      <c r="F12" t="n">
+        <v>86</v>
+      </c>
+      <c r="G12" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10460,6 +10550,15 @@
           <t>Pacific</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>89</v>
+      </c>
+      <c r="F13" t="n">
+        <v>86</v>
+      </c>
+      <c r="G13" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10482,6 +10581,15 @@
           <t>Atlantic</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>91</v>
+      </c>
+      <c r="F14" t="n">
+        <v>87</v>
+      </c>
+      <c r="G14" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10504,6 +10612,15 @@
           <t>Pacific</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>89</v>
+      </c>
+      <c r="F15" t="n">
+        <v>85</v>
+      </c>
+      <c r="G15" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10526,6 +10643,15 @@
           <t>Central</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>86</v>
+      </c>
+      <c r="F16" t="n">
+        <v>89</v>
+      </c>
+      <c r="G16" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10548,6 +10674,15 @@
           <t>Atlantic</t>
         </is>
       </c>
+      <c r="E17" t="n">
+        <v>91</v>
+      </c>
+      <c r="F17" t="n">
+        <v>88</v>
+      </c>
+      <c r="G17" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10570,6 +10705,15 @@
           <t>Central</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>87</v>
+      </c>
+      <c r="F18" t="n">
+        <v>84</v>
+      </c>
+      <c r="G18" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10623,6 +10767,15 @@
           <t>Metropolitan</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>87</v>
+      </c>
+      <c r="F20" t="n">
+        <v>89</v>
+      </c>
+      <c r="G20" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10645,6 +10798,15 @@
           <t>Metropolitan</t>
         </is>
       </c>
+      <c r="E21" t="n">
+        <v>85</v>
+      </c>
+      <c r="F21" t="n">
+        <v>87</v>
+      </c>
+      <c r="G21" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10667,6 +10829,15 @@
           <t>Atlantic</t>
         </is>
       </c>
+      <c r="E22" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22" t="n">
+        <v>83</v>
+      </c>
+      <c r="G22" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10689,6 +10860,15 @@
           <t>Metropolitan</t>
         </is>
       </c>
+      <c r="E23" t="n">
+        <v>87</v>
+      </c>
+      <c r="F23" t="n">
+        <v>84</v>
+      </c>
+      <c r="G23" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10711,6 +10891,15 @@
           <t>Metropolitan</t>
         </is>
       </c>
+      <c r="E24" t="n">
+        <v>90</v>
+      </c>
+      <c r="F24" t="n">
+        <v>84</v>
+      </c>
+      <c r="G24" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10733,6 +10922,15 @@
           <t>Pacific</t>
         </is>
       </c>
+      <c r="E25" t="n">
+        <v>87</v>
+      </c>
+      <c r="F25" t="n">
+        <v>82</v>
+      </c>
+      <c r="G25" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10755,6 +10953,15 @@
           <t>Pacific</t>
         </is>
       </c>
+      <c r="E26" t="n">
+        <v>86</v>
+      </c>
+      <c r="F26" t="n">
+        <v>85</v>
+      </c>
+      <c r="G26" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10777,6 +10984,15 @@
           <t>Central</t>
         </is>
       </c>
+      <c r="E27" t="n">
+        <v>86</v>
+      </c>
+      <c r="F27" t="n">
+        <v>84</v>
+      </c>
+      <c r="G27" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10799,6 +11015,15 @@
           <t>Atlantic</t>
         </is>
       </c>
+      <c r="E28" t="n">
+        <v>89</v>
+      </c>
+      <c r="F28" t="n">
+        <v>88</v>
+      </c>
+      <c r="G28" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10852,6 +11077,15 @@
           <t>Central</t>
         </is>
       </c>
+      <c r="E30" t="n">
+        <v>89</v>
+      </c>
+      <c r="F30" t="n">
+        <v>83</v>
+      </c>
+      <c r="G30" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10874,6 +11108,15 @@
           <t>Pacific</t>
         </is>
       </c>
+      <c r="E31" t="n">
+        <v>84</v>
+      </c>
+      <c r="F31" t="n">
+        <v>81</v>
+      </c>
+      <c r="G31" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10896,6 +11139,15 @@
           <t>Pacific</t>
         </is>
       </c>
+      <c r="E32" t="n">
+        <v>87</v>
+      </c>
+      <c r="F32" t="n">
+        <v>89</v>
+      </c>
+      <c r="G32" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10918,6 +11170,15 @@
           <t>Metropolitan</t>
         </is>
       </c>
+      <c r="E33" t="n">
+        <v>91</v>
+      </c>
+      <c r="F33" t="n">
+        <v>86</v>
+      </c>
+      <c r="G33" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10939,6 +11200,15 @@
         <is>
           <t>Central</t>
         </is>
+      </c>
+      <c r="E34" t="n">
+        <v>86</v>
+      </c>
+      <c r="F34" t="n">
+        <v>86</v>
+      </c>
+      <c r="G34" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -10952,7 +11222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11131,6 +11401,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Team ratings loaded for the remaining 30 clubs from the user's report; all 32 are now rated. NYI reads 87 offense / 89 defense / 93 goaltending.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -5385,7 +5385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYI is &lt;b&gt;1-0-1&lt;/b&gt; through two games, worth &lt;b&gt;3&lt;/b&gt; of a possible 4 points.</t>
+          <t>&lt;b&gt;Six&lt;/b&gt; different Islanders scored in G2 vs. NJD; the team had one goal in G1 at TOR.</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Six&lt;/b&gt; different Islanders scored in G2 vs. NJD; the team had one goal in G1 at TOR.</t>
+          <t>NYI took the 1st and the 3rd &lt;b&gt;3-0&lt;/b&gt; in G2 vs. NJD and lost the 2nd &lt;b&gt;1-0&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NYI took the 1st and the 3rd &lt;b&gt;3-0&lt;/b&gt; in G2 vs. NJD and lost the 2nd &lt;b&gt;1-0&lt;/b&gt;.</t>
+          <t>Three NYI minors in the 1st of G2 vs. NJD handed New Jersey two 5-on-3 power plays, the second of them 6 seconds long, and the only goal scored during either went the other way.</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Three straight NYI minors in the 1st of G2 vs. NJD put New Jersey two men up twice, and the only goal of that stretch went the other way.</t>
+          <t>NYI won G2 vs. NJD by five while being outshot &lt;b&gt;42-35&lt;/b&gt; and winning &lt;b&gt;14 of 46 faceoffs (30%)&lt;/b&gt;.</t>
         </is>
       </c>
     </row>
@@ -5493,16 +5493,6 @@
         <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
-        <is>
-          <t>NYI won G2 vs. NJD by five while being outshot &lt;b&gt;42-35&lt;/b&gt; and winning &lt;b&gt;14 of 46 faceoffs (30%)&lt;/b&gt;.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" t="inlineStr">
         <is>
           <t>The Isles have killed all &lt;b&gt;6&lt;/b&gt; power plays they have faced this season and are &lt;b&gt;1 for 7&lt;/b&gt; on their own, the goal coming in the 3rd of G2 vs. NJD.</t>
         </is>
@@ -5669,7 +5659,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Sorokin&lt;/b&gt; was beaten only when Bratt got to his own rebound in the 2nd of G2 vs. NJD, and has allowed three goals in two starts.</t>
+          <t>The only puck past &lt;b&gt;Sorokin&lt;/b&gt; in G2 vs. NJD was Bratt's own rebound in the 2nd; he is at three goals allowed through two starts.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5922,7 +5912,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COL 2028 R3; J. Nurmi (LW, $0.870M)</t>
+          <t>COL 2028 R3; J. Nurmi (LW, $0.87M)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3607,6 +3607,46 @@
       </c>
       <c r="K46" t="n">
         <v>201</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>K. Mandolese</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>In the System</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5794,7 +5834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5960,6 +6000,80 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>Declined</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Waivers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>K. Mandolese (G, $0.85M)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hamilton Hammers</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>To AHL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>K. Mandolese (G, $0.85M)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Accepted</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10872,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
         <v>89</v>
@@ -11212,7 +11326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11403,6 +11517,42 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Claimed G K. Mandolese off waivers (one year left at $0.85M) and assigned him to the Hamilton Hammers. Logged as two Transactions rows: the Waivers claim and the Assignment. Date is the franchise's current date (G2, 10/03/2026) - the user did not give one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mandolese's OVR, age and handedness are not in the workbook: the user reported the move, not the player screen. Blank rather than guessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NYI team ratings updated to 88 / 89 / 93 (was 87 / 89 / 93).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3572,6 +3572,46 @@
       <c r="F45" t="n">
         <v>93</v>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>31</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NMC</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="R45" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="T45" t="n">
+        <v>8.25</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3600,6 +3640,19 @@
       <c r="F46" t="n">
         <v>81</v>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>38</v>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>6'2"</t>
@@ -3608,44 +3661,339 @@
       <c r="K46" t="n">
         <v>201</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>M-NTC</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>UFA</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>UFA</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>V. Vanecek</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>In the System</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>77</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>30</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>UFA</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>UFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>K. Mandolese</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>In the System</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="F48" t="n">
+        <v>74</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Backup</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>26</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q48" t="n">
         <v>0.85</v>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>RFA</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>RFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>H. Tikkanen</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>In the System</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>68</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Fringe Starter</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>26</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>RFA</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>RFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>B. Hood</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>In the System</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>67</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>AHL Starter</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>19</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>UNSIGNED</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>UFA</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>UFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T. Lennox</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>In the System</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>65</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Fringe Starter</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>23</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>RFA</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6354,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6043,7 +6391,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7749,13 +8097,13 @@
         <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>88.75</v>
+        <v>99.75</v>
       </c>
       <c r="D3" t="n">
-        <v>15.24</v>
+        <v>18.79</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -7765,7 +8113,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>71.875</v>
+        <v>80.125</v>
       </c>
       <c r="D4" t="n">
         <v>4.875</v>
@@ -7778,7 +8126,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>56.4</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="D5" t="n">
         <v>2.15</v>
@@ -7794,7 +8142,7 @@
         <v>106.6</v>
       </c>
       <c r="C6" t="n">
-        <v>45.8</v>
+        <v>54.05</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -7915,7 +8263,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09/29/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8411,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>43/50</t>
+          <t>44/50</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11553,6 +11901,90 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Goalie contracts loaded from the List All Contracts screens (Goalies / Main Roster and Goalies / In the System). Sorokin $8.25M with an NMC, FSC Yes; Varlamov $2.75M with an M-NTC, UFA after 26-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Four system goalies the 09/29 seed never had: Vanecek 77, Tikkanen 68, Hood 67 (unsigned), Lennox 65. Mandolese reads 74 OVR, Backup/Med, age 26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sorokin's screen only shows 26-27 and 27-28 at $8.25M. 28-29 and 29-30 are derived, not photographed: the In the System screen's 29-30 footer reads $54.050M against $45.800M of skater salary, a difference of exactly $8.25M, and a contract cannot skip a year. 30-31 is left blank - the Cap sheet's contract counts (6 against 5 skaters) prove a goalie is signed that season and Sorokin is the only candidate, but the screen has not shown the figure. Needs the main roster goalie screen scrolled right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cap Outlook's Main Roster and System columns were skater-only; the goalie deals are folded in for 26-27 through 29-30. 30-31 and 31-32 still exclude Sorokin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The game counts 44 contracts; the workbook's own rows come to 45 (39 skaters plus 6 signed goalies). One contract on the list is not counting against the 50 and the screens do not say which.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RFA chips are orange (NON TENDERED) for Mandolese, Tikkanen and Lennox. The Roster Ref year columns hold the tag only, so tendered vs non-tendered has no home yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mandolese's waiver claim re-dated 10/03/2026 -&gt; 10/06/2026, the franchise's current date on the contract screens.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -4008,7 +4008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL4"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4575,6 +4575,152 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>31</v>
+      </c>
+      <c r="T5" t="n">
+        <v>44</v>
+      </c>
+      <c r="U5" t="n">
+        <v>37</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>03:12</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1/8</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1-1-1</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Out-shot New York 47-31 and drew eight power plays, but gave up three shorthanded goals and lost a game they had pulled level at 2-2 in the 3rd.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4586,7 +4732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5053,6 +5199,226 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>M. Rempe</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SHG</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>J. Veleno</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SHG</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>A. Romanov</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>M. Maccelli</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>E. Heineman</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>M. Barzal</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PPG</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>P. Dorofeyev</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SHG</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>A. Lafreniere</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5064,7 +5430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5235,6 +5601,51 @@
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>I. Sorokin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60:00</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
@@ -5585,7 +5996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5759,6 +6170,66 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>Mantha slashing. Bjugstad holding, 5-on-3. Coronato feeds Schenn (1), who finishes from above the hash in the right circle on the power play (4-1). Hischier interference. Cizikas (1) is credited after losing the puck at the side of the net and watching Bratt knock it into his own net (5-1). Maccelli (1) breaks away with two defensemen in tow and has hands down the slot on Rittich (6-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bjorkstrand charging. Rempe strips Barzal along the wall and beats Sorokin blocker side shorthanded (1-0). Veleno takes it off the boards after the Isles lose the puck in their own end and makes it two shorthanded goals in the period (2-0). Romanov (1) one-times Maccelli's pass from above the left dot out of the high slot (2-1). Dorofeyev elbowing. Sorokin leaves the ice behind his own net and takes a delay of game, 4-on-4. Cuylle slashing. Cizikas boarding, 4-on-4 again. Dorofeyev interference with 30 seconds left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Heineman slashing, more 4-on-4 to start the period. Palmieri hooking. Neither side scored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rempe charging at 12:06. Miller charging behind him, 5-on-3 for a minute, and Schneider penalized on top of it. Barzal finds Heineman (1) at the left post on the power play (2-2). Dorofeyev answers in alone on Sorokin with New York still a man down (3-2). Seven and a half minutes left. Lafreniere breaks in alone and has hands in close (4-2).</t>
         </is>
       </c>
     </row>
@@ -5773,7 +6244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5883,6 +6354,56 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>The Isles have killed all &lt;b&gt;6&lt;/b&gt; power plays they have faced this season and are &lt;b&gt;1 for 7&lt;/b&gt; on their own, the goal coming in the 3rd of G2 vs. NJD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Isles have killed all &lt;b&gt;10&lt;/b&gt; power plays they have faced this season, but New York scored &lt;b&gt;three&lt;/b&gt; shorthanded goals in G3 at NYR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NYI has out-shot its opponent once in three games, &lt;b&gt;47-31&lt;/b&gt; in G3 at NYR, and lost by two.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Eight power plays and &lt;b&gt;8:09&lt;/b&gt; with the extra man in G3 at NYR produced one goal. NYI is &lt;b&gt;2 for 15&lt;/b&gt; on the season, both goals in the 3rd period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NYI has won &lt;b&gt;48 of 123 faceoffs (39%)&lt;/b&gt; this season and &lt;b&gt;13 of 40&lt;/b&gt; in G3 at NYR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Five&lt;/b&gt; of the nine goals NYI has scored this season have come in the 1st period.</t>
         </is>
       </c>
     </row>
@@ -5897,7 +6418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6168,6 +6689,144 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>27</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Saves</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Sorokin&lt;/b&gt; stopped 27 of 31 in G3 at NYR and gave up four goals in a night after allowing three across his first two starts combined.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Goals</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Romanov&lt;/b&gt; one-timed Maccelli's feed out of the high slot in the 1st of G3 at NYR, the defenseman's first of the season and the only Islanders goal until the 3rd.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Goals</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Heineman&lt;/b&gt; finished Barzal's pass at the left post to pull G3 at NYR level at 2-2, the only goal NYI got out of eight power plays.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Assists</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Barzal&lt;/b&gt; picked up his first point of the season on the tying goal in the 3rd of G3 at NYR.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Maccelli&lt;/b&gt; has a point in each of the last two: the sixth goal in G2 vs. NJD and the feed to Romanov in G3 at NYR.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Horvat&lt;/b&gt;'s point streak ended at two in G3 at NYR.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>past</t>
         </is>
       </c>
     </row>
@@ -11674,7 +12333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11985,6 +12644,18 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>G3 at NYR: Team stats from the 1st and 2nd intermission screens and the final; per-period shots and hits differenced from the cumulative ones. Both box scores held for the screens. The Rangers goalie is not named anywhere, so Opp Goaltending has no row. New York's third shorthanded goal is assigned to Dorofeyev: the screens put SHG A at 2 after the 2nd and 3 at the final, NYR scored twice in the 3rd and took no power play in it, and Dorofeyev's came straight off the Heineman power-play goal with penalties still being served. Lafreniere's is logged even strength.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Declined</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Claimed</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12333,7 +12333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12656,6 +12656,18 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Transactions Result vocabulary is per Type: a Trade offer is Accepted / Declined, a Waivers row is Claimed / Passed, and an Assignment is '-' because a roster move has no accept-or-decline outcome to report - the same reason its Partner column holds '-' on a waiver claim.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/S1 NY Islanders.xlsx
+++ b/S1 NY Islanders.xlsx
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -12333,7 +12333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12664,7 +12664,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Transactions Result vocabulary is per Type: a Trade offer is Accepted / Declined, a Waivers row is Claimed / Passed, and an Assignment is '-' because a roster move has no accept-or-decline outcome to report - the same reason its Partner column holds '-' on a waiver claim.</t>
+          <t>Transactions Result vocabulary is per Type: a Trade offer is Accepted / Declined, a Waivers row is Claimed / Declined, and an Assignment is '-' because a roster move has no accept-or-decline outcome to report - the same reason its Partner column holds '-' on a waiver claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>'Passed' was not the game's word for a waiver a club does not claim - Declined is. The Result column takes the vocabulary the game and the sport use, never a synonym that reads better.</t>
         </is>
       </c>
     </row>
